--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131666524</v>
       </c>
       <c r="B2" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131666621</v>
       </c>
       <c r="B4" t="n">
-        <v>92287</v>
+        <v>92288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131666524</v>
       </c>
       <c r="B2" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131666571</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131666621</v>
       </c>
       <c r="B4" t="n">
-        <v>92288</v>
+        <v>92289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131666524</v>
       </c>
       <c r="B2" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131666571</v>
       </c>
       <c r="B3" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131666621</v>
       </c>
       <c r="B4" t="n">
-        <v>92289</v>
+        <v>92292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131666524</v>
       </c>
       <c r="B2" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131666571</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131666621</v>
       </c>
       <c r="B4" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131666524</v>
       </c>
       <c r="B2" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131666571</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131666621</v>
       </c>
       <c r="B4" t="n">
-        <v>92298</v>
+        <v>92301</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131666524</v>
       </c>
       <c r="B2" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131666571</v>
       </c>
       <c r="B3" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131666621</v>
       </c>
       <c r="B4" t="n">
-        <v>92301</v>
+        <v>92306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131666524</v>
+        <v>131666621</v>
       </c>
       <c r="B2" t="n">
-        <v>99095</v>
+        <v>92406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Slånget, Slånget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525789</v>
+        <v>525781</v>
       </c>
       <c r="R2" t="n">
-        <v>6717906</v>
+        <v>6717863</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,41 +782,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131666571</v>
+        <v>131666524</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>99195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Slånget, Slånget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525811</v>
+        <v>525789</v>
       </c>
       <c r="R3" t="n">
-        <v>6717837</v>
+        <v>6717906</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,113 +900,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>131666621</v>
-      </c>
-      <c r="B4" t="n">
-        <v>92349</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Slånget, Slånget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>525781</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6717863</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Stora Kopparberg</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>FREDRIK Månsson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>FREDRIK Månsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36966-2022 artfynd.xlsx
+++ b/artfynd/A 36966-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131666621</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,8 +910,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131666524</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>